--- a/NBFC-MF/Borrowers/Konsam_Ranjana_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Konsam_Ranjana_Weekly.xlsx
@@ -861,31 +861,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
+      <c r="A5" s="19">
+        <v>46279</v>
+      </c>
+      <c r="B5" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>339.7255840979721</v>
+      </c>
+      <c r="F5" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>1060.2744159020278</v>
+      </c>
+      <c r="G5" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>15882.325006125111</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>4117.674993874889</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -1122,7 +1124,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1157,7 +1159,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>19600</v>
+        <v>18200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1192,7 +1194,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>16942.599422027139</v>
+        <v>15882.325006125111</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1227,7 +1229,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3057.4005779728614</v>
+        <v>4117.674993874889</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Konsam_Ranjana_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Konsam_Ranjana_Weekly.xlsx
@@ -895,31 +895,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
+      <c r="A6" s="2">
+        <v>46288</v>
+      </c>
+      <c r="B6" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>318.4654258262637</v>
+      </c>
+      <c r="F6" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
+        <v>1081.5345741737362</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>14800.790431951375</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>5199.2095680486254</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -927,31 +929,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
+      <c r="A7" s="19">
+        <v>46293</v>
+      </c>
+      <c r="B7" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>296.77896817115123</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
+        <v>1103.2210318288487</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>13697.569400122526</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>6302.4305998774744</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1124,7 +1128,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>18200</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1194,7 +1198,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>15882.325006125111</v>
+        <v>13697.569400122526</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1229,7 +1233,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>4117.674993874889</v>
+        <v>6302.4305998774744</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Konsam_Ranjana_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Konsam_Ranjana_Weekly.xlsx
@@ -965,31 +965,33 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
+      <c r="A8" s="2">
+        <v>46300</v>
+      </c>
+      <c r="B8" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>274.657663164084</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
+        <v>1125.3423368359161</v>
+      </c>
+      <c r="G8" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>12572.227063286609</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>7427.7729367133907</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1000,31 +1002,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
+      <c r="A9" s="19">
+        <v>46307</v>
+      </c>
+      <c r="B9" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>252.09279143638921</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
+        <v>1147.9072085636108</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>11424.319854722999</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>8575.6801452770014</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1128,7 +1132,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1163,7 +1167,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>15400</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1198,7 +1202,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>13697.569400122526</v>
+        <v>11424.319854722999</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1233,7 +1237,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>6302.4305998774744</v>
+        <v>8575.6801452770014</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
